--- a/docs/Logic Requirements/Ageipelago El Cid.xlsx
+++ b/docs/Logic Requirements/Ageipelago El Cid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B10145-77F0-44B5-BB7A-537F49BA6BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B5942C-069B-46F2-A27B-CF81168B65CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="201">
   <si>
     <t>Scenario</t>
   </si>
@@ -3877,12 +3877,47 @@
       <t>(Not on Standard)</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <t>No Sappers
+No Fortifed Wall</t>
+  </si>
+  <si>
+    <t>No Fortified Wall
+No Fortified Gate</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4080,6 +4115,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4095,7 +4137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -4231,11 +4273,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4363,9 +4429,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4379,6 +4442,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5015,15 +5105,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7806EE9-C3B6-4767-BE4E-BC3AB2AED020}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5037,7 +5133,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="37" t="s">
         <v>118</v>
       </c>
@@ -5051,7 +5152,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G4" s="22" t="s">
         <v>114</v>
       </c>
@@ -5065,7 +5175,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>196</v>
+      </c>
       <c r="G5" s="26" t="s">
         <v>77</v>
       </c>
@@ -5079,7 +5198,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
       <c r="G6" s="14" t="s">
         <v>123</v>
       </c>
@@ -5093,7 +5215,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
       <c r="G7" s="26" t="s">
         <v>124</v>
       </c>
@@ -5107,7 +5232,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
       <c r="G8" s="23" t="s">
         <v>111</v>
       </c>
@@ -5121,7 +5249,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="23" t="s">
         <v>78</v>
       </c>
@@ -5135,7 +5266,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="23" t="s">
         <v>121</v>
       </c>
@@ -5149,7 +5283,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="G11" s="23" t="s">
         <v>93</v>
       </c>
@@ -5163,7 +5300,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
       <c r="G12" s="24" t="s">
         <v>122</v>
       </c>
@@ -5177,7 +5317,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
       <c r="G13" s="23" t="s">
         <v>126</v>
       </c>
@@ -5191,7 +5334,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
       <c r="G14" s="23" t="s">
         <v>104</v>
       </c>
@@ -5205,7 +5351,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
       <c r="G15" s="23" t="s">
         <v>127</v>
       </c>
@@ -5219,7 +5368,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
       <c r="G16" s="23" t="s">
         <v>128</v>
       </c>
@@ -5438,6 +5590,10 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5447,18 +5603,21 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="0.140625" customWidth="1"/>
-    <col min="3" max="3" width="69.85546875" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="47.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5472,7 +5631,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="3:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="37" t="s">
         <v>116</v>
       </c>
@@ -5486,7 +5650,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G4" s="30" t="s">
         <v>111</v>
       </c>
@@ -5500,7 +5673,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>196</v>
+      </c>
       <c r="G5" s="31" t="s">
         <v>104</v>
       </c>
@@ -5514,7 +5696,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
       <c r="G6" s="31" t="s">
         <v>137</v>
       </c>
@@ -5528,7 +5713,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
       <c r="G7" s="31" t="s">
         <v>101</v>
       </c>
@@ -5542,7 +5730,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
       <c r="G8" s="10" t="s">
         <v>139</v>
       </c>
@@ -5556,7 +5747,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="31" t="s">
         <v>121</v>
       </c>
@@ -5570,7 +5764,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="20" t="s">
         <v>140</v>
       </c>
@@ -5584,8 +5781,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="3:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="C11" s="10" t="s">
+    <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
+      <c r="F11" s="10" t="s">
         <v>145</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -5601,8 +5801,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="C12" s="10" t="s">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
+      <c r="F12" s="10" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="20" t="s">
@@ -5618,8 +5821,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="C13" s="10" t="s">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
+      <c r="F13" s="10" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -5635,8 +5841,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="3:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="10" t="s">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
+      <c r="F14" s="10" t="s">
         <v>147</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -5652,8 +5861,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="44" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="43" t="s">
         <v>84</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -5666,7 +5878,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="3:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
       <c r="G16" s="32" t="s">
         <v>149</v>
       </c>
@@ -5681,7 +5896,7 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="45" t="s">
         <v>150</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -5873,21 +6088,31 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CC0715-C907-4E5C-AD21-1C53B8AEFAF6}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5901,7 +6126,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="7" t="s">
         <v>116</v>
       </c>
@@ -5915,7 +6145,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>114</v>
       </c>
@@ -5929,8 +6168,17 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="45" t="s">
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>152</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -5943,7 +6191,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
       <c r="G6" s="23" t="s">
         <v>127</v>
       </c>
@@ -5957,7 +6208,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
       <c r="G7" s="23" t="s">
         <v>128</v>
       </c>
@@ -5971,7 +6225,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
       <c r="G8" s="23" t="s">
         <v>91</v>
       </c>
@@ -5985,7 +6242,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="23" t="s">
         <v>78</v>
       </c>
@@ -5999,7 +6259,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="23" t="s">
         <v>124</v>
       </c>
@@ -6013,7 +6276,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="G11" s="32" t="s">
         <v>140</v>
       </c>
@@ -6027,7 +6293,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
       <c r="G12" s="32" t="s">
         <v>153</v>
       </c>
@@ -6041,8 +6310,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="46" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="45" t="s">
         <v>155</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -6055,7 +6327,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
       <c r="G14" s="33" t="s">
         <v>126</v>
       </c>
@@ -6069,7 +6344,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
       <c r="G15" s="33" t="s">
         <v>101</v>
       </c>
@@ -6083,7 +6361,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
       <c r="G16" s="33" t="s">
         <v>104</v>
       </c>
@@ -6140,7 +6421,7 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="45" t="s">
         <v>156</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -6294,21 +6575,31 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D504A7F2-3BD6-44D6-BE88-D138677C7901}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6322,7 +6613,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="10" t="s">
         <v>118</v>
       </c>
@@ -6336,7 +6632,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>114</v>
       </c>
@@ -6350,7 +6655,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>198</v>
+      </c>
       <c r="G5" s="38" t="s">
         <v>121</v>
       </c>
@@ -6364,7 +6678,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
       <c r="G6" s="32" t="s">
         <v>140</v>
       </c>
@@ -6378,7 +6695,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
       <c r="G7" s="32" t="s">
         <v>153</v>
       </c>
@@ -6392,8 +6712,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="47" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="46" t="s">
         <v>158</v>
       </c>
       <c r="H8" s="9" t="s">
@@ -6406,7 +6729,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="32" t="s">
         <v>93</v>
       </c>
@@ -6420,7 +6746,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="32" t="s">
         <v>111</v>
       </c>
@@ -6434,7 +6763,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="G11" s="32" t="s">
         <v>101</v>
       </c>
@@ -6448,7 +6780,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
       <c r="G12" s="20" t="s">
         <v>159</v>
       </c>
@@ -6462,7 +6797,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
       <c r="G13" s="20" t="s">
         <v>149</v>
       </c>
@@ -6476,7 +6814,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
       <c r="G14" s="20" t="s">
         <v>161</v>
       </c>
@@ -6490,7 +6831,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
       <c r="G15" s="20" t="s">
         <v>162</v>
       </c>
@@ -6504,7 +6848,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
       <c r="G16" s="20" t="s">
         <v>163</v>
       </c>
@@ -6751,21 +7098,31 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBE6260-452E-4DFF-B03C-024D06C3012A}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6779,7 +7136,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="25" t="s">
         <v>118</v>
       </c>
@@ -6793,21 +7155,39 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G4" s="33" t="s">
         <v>128</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="45" t="s">
         <v>89</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>196</v>
+      </c>
       <c r="G5" s="33" t="s">
         <v>127</v>
       </c>
@@ -6821,7 +7201,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
       <c r="G6" s="33" t="s">
         <v>78</v>
       </c>
@@ -6835,8 +7218,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="46" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="45" t="s">
         <v>107</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -6849,7 +7235,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
       <c r="G8" s="33" t="s">
         <v>121</v>
       </c>
@@ -6863,7 +7252,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="33" t="s">
         <v>91</v>
       </c>
@@ -6877,7 +7269,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="33" t="s">
         <v>101</v>
       </c>
@@ -6891,7 +7286,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="G11" s="33" t="s">
         <v>88</v>
       </c>
@@ -6905,7 +7303,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
       <c r="G12" s="33" t="s">
         <v>111</v>
       </c>
@@ -6919,7 +7320,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
       <c r="G13" s="33" t="s">
         <v>137</v>
       </c>
@@ -6933,8 +7337,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="46" t="s">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="45" t="s">
         <v>175</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -6947,7 +7354,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
       <c r="G15" s="33" t="s">
         <v>77</v>
       </c>
@@ -6961,8 +7371,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="46" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="45" t="s">
         <v>76</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -6990,7 +7403,7 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="45" t="s">
         <v>176</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -7176,21 +7589,31 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872C15AD-8AB7-49C1-937E-3B0C304F5546}">
-  <dimension ref="D1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="4:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -7204,50 +7627,76 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="36" t="s">
         <v>163</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="47" t="s">
         <v>184</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="47" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="46" t="s">
         <v>97</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="46" t="s">
         <v>185</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>196</v>
+      </c>
       <c r="G5" s="32" t="s">
         <v>88</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="46" t="s">
         <v>186</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="47" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="46" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -7260,7 +7709,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="13"/>
       <c r="G7" s="26" t="s">
         <v>111</v>
       </c>
@@ -7274,7 +7726,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="13"/>
       <c r="G8" s="26" t="s">
         <v>93</v>
       </c>
@@ -7288,7 +7743,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="13"/>
       <c r="G9" s="26" t="s">
         <v>82</v>
       </c>
@@ -7302,7 +7760,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="13"/>
       <c r="G10" s="26" t="s">
         <v>183</v>
       </c>
@@ -7316,8 +7777,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D11" s="43"/>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="G11" s="14" t="s">
         <v>179</v>
       </c>
@@ -7331,7 +7794,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="13"/>
       <c r="G12" s="26" t="s">
         <v>162</v>
       </c>
@@ -7345,7 +7811,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="13"/>
       <c r="G13" s="26" t="s">
         <v>161</v>
       </c>
@@ -7359,7 +7828,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="13"/>
       <c r="G14" s="10" t="s">
         <v>181</v>
       </c>
@@ -7373,7 +7845,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="13"/>
       <c r="G15" s="26" t="s">
         <v>164</v>
       </c>
@@ -7387,7 +7862,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="13"/>
       <c r="G16" s="20" t="s">
         <v>180</v>
       </c>
@@ -7432,7 +7910,7 @@
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="43" t="s">
         <v>187</v>
       </c>
       <c r="L19" s="9" t="s">
@@ -7578,6 +8056,10 @@
       <c r="L42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago El Cid.xlsx
+++ b/docs/Logic Requirements/Ageipelago El Cid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B5942C-069B-46F2-A27B-CF81168B65CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F62383-0736-4928-A7E4-41229814DDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
   </bookViews>
   <sheets>
     <sheet name="El Cid" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="203">
   <si>
     <t>Scenario</t>
   </si>
@@ -3912,12 +3912,60 @@
   <si>
     <t>Castle - Imperial Age</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes are researched automatically</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No Sappers
+No Fortifed Wall
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes are researched automatically</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4121,6 +4169,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4444,6 +4498,15 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4460,15 +4523,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5115,11 +5169,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5134,11 +5188,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="37" t="s">
         <v>118</v>
       </c>
@@ -5175,15 +5229,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
-        <v>196</v>
+      <c r="D5" s="48" t="s">
+        <v>201</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>77</v>
@@ -5199,8 +5253,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="14" t="s">
         <v>123</v>
@@ -5216,8 +5270,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="26" t="s">
         <v>124</v>
@@ -5233,8 +5287,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="23" t="s">
         <v>111</v>
@@ -5250,8 +5304,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="23" t="s">
         <v>78</v>
@@ -5267,8 +5321,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="23" t="s">
         <v>121</v>
@@ -5284,8 +5338,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="G11" s="23" t="s">
         <v>93</v>
@@ -5301,8 +5355,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="G12" s="24" t="s">
         <v>122</v>
@@ -5318,8 +5372,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="G13" s="23" t="s">
         <v>126</v>
@@ -5335,8 +5389,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="G14" s="23" t="s">
         <v>104</v>
@@ -5352,8 +5406,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="23" t="s">
         <v>127</v>
@@ -5369,8 +5423,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="23" t="s">
         <v>128</v>
@@ -5595,12 +5649,13 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE5F8DB-FD15-4784-84F9-B75AFD37E946}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -5613,11 +5668,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5632,11 +5687,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="37" t="s">
         <v>116</v>
       </c>
@@ -5674,13 +5729,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="48" t="s">
         <v>196</v>
       </c>
       <c r="G5" s="31" t="s">
@@ -5697,8 +5752,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="31" t="s">
         <v>137</v>
@@ -5714,8 +5769,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="31" t="s">
         <v>101</v>
@@ -5731,8 +5786,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="10" t="s">
         <v>139</v>
@@ -5748,8 +5803,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="31" t="s">
         <v>121</v>
@@ -5765,8 +5820,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="20" t="s">
         <v>140</v>
@@ -5782,8 +5837,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="F11" s="10" t="s">
         <v>145</v>
@@ -5802,8 +5857,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="F12" s="10" t="s">
         <v>146</v>
@@ -5822,8 +5877,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="F13" s="10" t="s">
         <v>148</v>
@@ -5842,8 +5897,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="F14" s="10" t="s">
         <v>147</v>
@@ -5862,8 +5917,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="43" t="s">
         <v>84</v>
@@ -5879,8 +5934,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="32" t="s">
         <v>149</v>
@@ -6108,11 +6163,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6127,11 +6182,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="7" t="s">
         <v>116</v>
       </c>
@@ -6169,13 +6224,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="48" t="s">
         <v>198</v>
       </c>
       <c r="G5" s="44" t="s">
@@ -6192,8 +6247,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="23" t="s">
         <v>127</v>
@@ -6209,8 +6264,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="23" t="s">
         <v>128</v>
@@ -6226,8 +6281,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="23" t="s">
         <v>91</v>
@@ -6243,8 +6298,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="23" t="s">
         <v>78</v>
@@ -6260,8 +6315,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="23" t="s">
         <v>124</v>
@@ -6277,8 +6332,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="G11" s="32" t="s">
         <v>140</v>
@@ -6294,8 +6349,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="G12" s="32" t="s">
         <v>153</v>
@@ -6311,8 +6366,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="G13" s="45" t="s">
         <v>155</v>
@@ -6328,8 +6383,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="G14" s="33" t="s">
         <v>126</v>
@@ -6345,8 +6400,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="33" t="s">
         <v>101</v>
@@ -6362,8 +6417,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="33" t="s">
         <v>104</v>
@@ -6595,11 +6650,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6614,11 +6669,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="10" t="s">
         <v>118</v>
       </c>
@@ -6655,15 +6710,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
-        <v>198</v>
+      <c r="D5" s="48" t="s">
+        <v>202</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>121</v>
@@ -6679,8 +6734,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="32" t="s">
         <v>140</v>
@@ -6696,8 +6751,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="32" t="s">
         <v>153</v>
@@ -6713,8 +6768,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="46" t="s">
         <v>158</v>
@@ -6730,8 +6785,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="32" t="s">
         <v>93</v>
@@ -6747,8 +6802,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="32" t="s">
         <v>111</v>
@@ -6764,8 +6819,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="G11" s="32" t="s">
         <v>101</v>
@@ -6781,8 +6836,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="G12" s="20" t="s">
         <v>159</v>
@@ -6798,8 +6853,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="G13" s="20" t="s">
         <v>149</v>
@@ -6815,8 +6870,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="G14" s="20" t="s">
         <v>161</v>
@@ -6832,8 +6887,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="20" t="s">
         <v>162</v>
@@ -6849,8 +6904,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="20" t="s">
         <v>163</v>
@@ -7118,11 +7173,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -7137,11 +7192,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="25" t="s">
         <v>118</v>
       </c>
@@ -7179,13 +7234,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="48" t="s">
         <v>196</v>
       </c>
       <c r="G5" s="33" t="s">
@@ -7202,8 +7257,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="33" t="s">
         <v>78</v>
@@ -7219,8 +7274,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="45" t="s">
         <v>107</v>
@@ -7236,8 +7291,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="33" t="s">
         <v>121</v>
@@ -7253,8 +7308,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="33" t="s">
         <v>91</v>
@@ -7270,8 +7325,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="33" t="s">
         <v>101</v>
@@ -7287,8 +7342,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="G11" s="33" t="s">
         <v>88</v>
@@ -7304,8 +7359,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="G12" s="33" t="s">
         <v>111</v>
@@ -7321,8 +7376,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="G13" s="33" t="s">
         <v>137</v>
@@ -7338,8 +7393,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="G14" s="45" t="s">
         <v>175</v>
@@ -7355,8 +7410,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="33" t="s">
         <v>77</v>
@@ -7372,8 +7427,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="45" t="s">
         <v>76</v>
@@ -7609,11 +7664,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -7628,11 +7683,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="36" t="s">
         <v>163</v>
       </c>
@@ -7670,13 +7725,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="48" t="s">
         <v>196</v>
       </c>
       <c r="G5" s="32" t="s">
@@ -7693,8 +7748,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="13"/>
       <c r="G6" s="46" t="s">
         <v>99</v>
@@ -7710,8 +7765,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="13"/>
       <c r="G7" s="26" t="s">
         <v>111</v>
@@ -7727,8 +7782,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="13"/>
       <c r="G8" s="26" t="s">
         <v>93</v>
@@ -7744,8 +7799,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="13"/>
       <c r="G9" s="26" t="s">
         <v>82</v>
@@ -7761,8 +7816,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="13"/>
       <c r="G10" s="26" t="s">
         <v>183</v>
@@ -7778,8 +7833,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="13"/>
       <c r="G11" s="14" t="s">
         <v>179</v>
@@ -7795,8 +7850,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="13"/>
       <c r="G12" s="26" t="s">
         <v>162</v>
@@ -7812,8 +7867,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="13"/>
       <c r="G13" s="26" t="s">
         <v>161</v>
@@ -7829,8 +7884,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="13"/>
       <c r="G14" s="10" t="s">
         <v>181</v>
@@ -7846,8 +7901,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="13"/>
       <c r="G15" s="26" t="s">
         <v>164</v>
@@ -7863,8 +7918,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="13"/>
       <c r="G16" s="20" t="s">
         <v>180</v>

--- a/docs/Logic Requirements/Ageipelago El Cid.xlsx
+++ b/docs/Logic Requirements/Ageipelago El Cid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F62383-0736-4928-A7E4-41229814DDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B430092-A59D-4BA2-BB58-E4AD9FFBF773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{B8266A09-EF6B-4D9A-952F-8D97365221FC}"/>
   </bookViews>
   <sheets>
     <sheet name="El Cid" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="217">
   <si>
     <t>Scenario</t>
   </si>
@@ -3959,6 +3959,48 @@
       <t>:
 Murder Holes are researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>El Cid Campeador</t>
+  </si>
+  <si>
+    <t>Trebuchet (Only on Standard</t>
+  </si>
+  <si>
+    <t>Castle (Only on Standard)</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Fire Ship (Not on Standard)</t>
+  </si>
+  <si>
+    <t>Fast Fire Ship (Only on Standard)</t>
+  </si>
+  <si>
+    <t>Pikeman (Not on Hard)</t>
+  </si>
+  <si>
+    <t>Battering Ram (Only on Hard)</t>
+  </si>
+  <si>
+    <t>Capped Ram (Only on Moderate)</t>
+  </si>
+  <si>
+    <t>Siege Ram (Only on Standard)</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -4351,11 +4393,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4504,9 +4557,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4523,6 +4573,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5163,17 +5222,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5188,11 +5248,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="37" t="s">
         <v>118</v>
       </c>
@@ -5269,7 +5329,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -5286,10 +5346,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="23" t="s">
         <v>111</v>
       </c>
@@ -5304,9 +5373,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>102</v>
+      </c>
       <c r="G9" s="23" t="s">
         <v>78</v>
       </c>
@@ -5321,9 +5397,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="58" t="s">
+        <v>106</v>
+      </c>
       <c r="G10" s="23" t="s">
         <v>121</v>
       </c>
@@ -5338,9 +5419,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>112</v>
+      </c>
       <c r="G11" s="23" t="s">
         <v>93</v>
       </c>
@@ -5355,9 +5441,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="57"/>
       <c r="G12" s="24" t="s">
         <v>122</v>
       </c>
@@ -5372,9 +5461,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="57"/>
       <c r="G13" s="23" t="s">
         <v>126</v>
       </c>
@@ -5389,9 +5481,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="57"/>
       <c r="G14" s="23" t="s">
         <v>104</v>
       </c>
@@ -5406,9 +5501,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="57"/>
       <c r="G15" s="23" t="s">
         <v>127</v>
       </c>
@@ -5423,9 +5521,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="57"/>
       <c r="G16" s="23" t="s">
         <v>128</v>
       </c>
@@ -5439,7 +5540,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="57"/>
       <c r="G17" s="23" t="s">
         <v>129</v>
       </c>
@@ -5453,7 +5560,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="57"/>
       <c r="G18" s="24" t="s">
         <v>130</v>
       </c>
@@ -5467,7 +5580,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="57"/>
       <c r="G19" s="23" t="s">
         <v>91</v>
       </c>
@@ -5481,7 +5600,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="57"/>
       <c r="G20" s="27" t="s">
         <v>101</v>
       </c>
@@ -5495,7 +5620,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="24" t="s">
         <v>132</v>
       </c>
@@ -5509,7 +5638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="K22" s="26" t="s">
@@ -5519,7 +5648,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="K23" s="26" t="s">
@@ -5529,7 +5658,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
       <c r="K24" s="18" t="s">
@@ -5539,49 +5668,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="K26" s="28"/>
       <c r="L26" s="28"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="K27" s="28"/>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
@@ -5660,7 +5789,7 @@
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="47.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
@@ -5668,11 +5797,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -5687,11 +5816,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="37" t="s">
         <v>116</v>
       </c>
@@ -5768,7 +5897,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -5785,10 +5914,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="10" t="s">
         <v>139</v>
       </c>
@@ -5803,9 +5941,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="57"/>
       <c r="G9" s="31" t="s">
         <v>121</v>
       </c>
@@ -5820,9 +5963,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="20" t="s">
         <v>140</v>
       </c>
@@ -5837,10 +5983,13 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
-      <c r="F11" s="10" t="s">
+      <c r="B11" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="9" t="s">
         <v>145</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -5857,10 +6006,13 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
-      <c r="F12" s="10" t="s">
+      <c r="B12" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="9" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="20" t="s">
@@ -5877,10 +6029,13 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
-      <c r="F13" s="10" t="s">
+      <c r="B13" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="9" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -5897,10 +6052,13 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
-      <c r="F14" s="10" t="s">
+      <c r="B14" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -5917,9 +6075,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
       <c r="G15" s="43" t="s">
         <v>84</v>
       </c>
@@ -5934,9 +6093,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="G16" s="32" t="s">
         <v>149</v>
       </c>
@@ -5950,7 +6110,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="45" t="s">
         <v>150</v>
       </c>
@@ -5964,7 +6128,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="28"/>
       <c r="H18" s="28"/>
       <c r="K18" s="31" t="s">
@@ -5974,7 +6142,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="28"/>
       <c r="H19" s="28"/>
       <c r="K19" s="31" t="s">
@@ -5984,7 +6156,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="28"/>
       <c r="H20" s="28"/>
       <c r="K20" s="31" t="s">
@@ -5994,7 +6170,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
       <c r="K21" s="31" t="s">
@@ -6004,7 +6184,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="K22" s="31" t="s">
@@ -6014,7 +6194,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="K23" s="31" t="s">
@@ -6024,7 +6204,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
       <c r="K24" s="20" t="s">
@@ -6034,7 +6214,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="K25" s="35" t="s">
@@ -6044,43 +6224,43 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="K27" s="28"/>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
@@ -6157,17 +6337,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6182,11 +6363,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="7" t="s">
         <v>116</v>
       </c>
@@ -6263,7 +6444,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -6280,10 +6461,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="23" t="s">
         <v>91</v>
       </c>
@@ -6298,9 +6488,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>113</v>
+      </c>
       <c r="G9" s="23" t="s">
         <v>78</v>
       </c>
@@ -6315,9 +6512,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>108</v>
+      </c>
       <c r="G10" s="23" t="s">
         <v>124</v>
       </c>
@@ -6332,9 +6534,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>105</v>
+      </c>
       <c r="G11" s="32" t="s">
         <v>140</v>
       </c>
@@ -6349,9 +6556,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>96</v>
+      </c>
       <c r="G12" s="32" t="s">
         <v>153</v>
       </c>
@@ -6366,9 +6578,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="57"/>
       <c r="G13" s="45" t="s">
         <v>155</v>
       </c>
@@ -6383,9 +6598,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="57"/>
       <c r="G14" s="33" t="s">
         <v>126</v>
       </c>
@@ -6400,9 +6618,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="57"/>
       <c r="G15" s="33" t="s">
         <v>101</v>
       </c>
@@ -6417,9 +6638,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="57"/>
       <c r="G16" s="33" t="s">
         <v>104</v>
       </c>
@@ -6433,7 +6657,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="33" t="s">
         <v>121</v>
       </c>
@@ -6447,7 +6675,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="33" t="s">
         <v>93</v>
       </c>
@@ -6461,7 +6693,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="33" t="s">
         <v>109</v>
       </c>
@@ -6475,7 +6711,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="45" t="s">
         <v>156</v>
       </c>
@@ -6489,7 +6729,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
       <c r="K21" s="34" t="s">
@@ -6499,7 +6743,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="K22" s="33" t="s">
@@ -6509,7 +6753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="K23" s="33" t="s">
@@ -6519,55 +6763,55 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
       <c r="K24" s="28"/>
       <c r="L24" s="28"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="K25" s="28"/>
       <c r="L25" s="28"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="K26" s="28"/>
       <c r="L26" s="28"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="K27" s="28"/>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
@@ -6644,17 +6888,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -6669,11 +6914,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="10" t="s">
         <v>118</v>
       </c>
@@ -6750,7 +6995,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -6767,10 +7012,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="46" t="s">
         <v>158</v>
       </c>
@@ -6785,9 +7039,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>96</v>
+      </c>
       <c r="G9" s="32" t="s">
         <v>93</v>
       </c>
@@ -6802,9 +7063,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>105</v>
+      </c>
       <c r="G10" s="32" t="s">
         <v>111</v>
       </c>
@@ -6819,9 +7087,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="56" t="s">
+        <v>108</v>
+      </c>
       <c r="G11" s="32" t="s">
         <v>101</v>
       </c>
@@ -6836,9 +7109,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="56" t="s">
+        <v>103</v>
+      </c>
       <c r="G12" s="20" t="s">
         <v>159</v>
       </c>
@@ -6853,9 +7131,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="56" t="s">
+        <v>95</v>
+      </c>
       <c r="G13" s="20" t="s">
         <v>149</v>
       </c>
@@ -6870,9 +7153,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="56" t="s">
+        <v>106</v>
+      </c>
       <c r="G14" s="20" t="s">
         <v>161</v>
       </c>
@@ -6887,9 +7173,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="56" t="s">
+        <v>110</v>
+      </c>
       <c r="G15" s="20" t="s">
         <v>162</v>
       </c>
@@ -6904,9 +7193,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="48" t="s">
+        <v>209</v>
+      </c>
       <c r="G16" s="20" t="s">
         <v>163</v>
       </c>
@@ -6920,7 +7212,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="20" t="s">
         <v>88</v>
       </c>
@@ -6934,7 +7230,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="26" t="s">
         <v>164</v>
       </c>
@@ -6948,7 +7248,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="26" t="s">
         <v>165</v>
       </c>
@@ -6962,7 +7266,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="26" t="s">
         <v>127</v>
       </c>
@@ -6976,7 +7284,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="26" t="s">
         <v>79</v>
       </c>
@@ -6990,7 +7302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="26" t="s">
         <v>91</v>
       </c>
@@ -7004,7 +7316,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="10" t="s">
         <v>166</v>
       </c>
@@ -7018,7 +7330,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="10" t="s">
         <v>168</v>
       </c>
@@ -7032,7 +7344,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="39" t="s">
         <v>167</v>
       </c>
@@ -7046,7 +7358,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="27" t="s">
         <v>128</v>
       </c>
@@ -7060,37 +7372,37 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="40"/>
       <c r="H27" s="16"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
@@ -7167,17 +7479,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -7192,11 +7505,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="25" t="s">
         <v>118</v>
       </c>
@@ -7273,7 +7586,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -7290,10 +7603,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="33" t="s">
         <v>121</v>
       </c>
@@ -7308,9 +7630,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>96</v>
+      </c>
       <c r="G9" s="33" t="s">
         <v>91</v>
       </c>
@@ -7325,9 +7654,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>105</v>
+      </c>
       <c r="G10" s="33" t="s">
         <v>101</v>
       </c>
@@ -7342,9 +7676,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>113</v>
+      </c>
       <c r="G11" s="33" t="s">
         <v>88</v>
       </c>
@@ -7359,9 +7698,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>102</v>
+      </c>
       <c r="G12" s="33" t="s">
         <v>111</v>
       </c>
@@ -7376,9 +7720,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>95</v>
+      </c>
       <c r="G13" s="33" t="s">
         <v>137</v>
       </c>
@@ -7393,9 +7742,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>106</v>
+      </c>
       <c r="G14" s="45" t="s">
         <v>175</v>
       </c>
@@ -7410,9 +7764,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>98</v>
+      </c>
       <c r="G15" s="33" t="s">
         <v>77</v>
       </c>
@@ -7427,9 +7786,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58" t="s">
+        <v>85</v>
+      </c>
       <c r="G16" s="45" t="s">
         <v>76</v>
       </c>
@@ -7443,7 +7805,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="56" t="s">
+        <v>96</v>
+      </c>
       <c r="G17" s="33" t="s">
         <v>126</v>
       </c>
@@ -7457,7 +7825,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="56" t="s">
+        <v>108</v>
+      </c>
       <c r="G18" s="45" t="s">
         <v>176</v>
       </c>
@@ -7471,7 +7845,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="56" t="s">
+        <v>105</v>
+      </c>
       <c r="G19" s="15" t="s">
         <v>177</v>
       </c>
@@ -7485,7 +7865,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="56" t="s">
+        <v>95</v>
+      </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="K20" s="20" t="s">
@@ -7495,7 +7881,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="56" t="s">
+        <v>110</v>
+      </c>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
       <c r="K21" s="20" t="s">
@@ -7505,7 +7897,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E22" s="56" t="s">
+        <v>103</v>
+      </c>
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="K22" s="31" t="s">
@@ -7515,7 +7910,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E23" s="48" t="s">
+        <v>94</v>
+      </c>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="K23" s="31" t="s">
@@ -7525,7 +7923,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E24" s="57"/>
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
       <c r="K24" s="31" t="s">
@@ -7535,7 +7934,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="E25" s="57"/>
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="K25" s="15" t="s">
@@ -7545,43 +7945,45 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E26" s="57"/>
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E27" s="57"/>
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="K27" s="28"/>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
@@ -7658,17 +8060,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
@@ -7683,11 +8086,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="36" t="s">
         <v>163</v>
       </c>
@@ -7764,7 +8167,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="13"/>
@@ -7781,10 +8184,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="13"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="G8" s="26" t="s">
         <v>93</v>
       </c>
@@ -7799,9 +8211,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="57"/>
+      <c r="E9" s="48" t="s">
+        <v>102</v>
+      </c>
       <c r="G9" s="26" t="s">
         <v>82</v>
       </c>
@@ -7816,9 +8235,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="26" t="s">
         <v>183</v>
       </c>
@@ -7832,10 +8256,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="13"/>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
       <c r="G11" s="14" t="s">
         <v>179</v>
       </c>
@@ -7850,9 +8279,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
       <c r="G12" s="26" t="s">
         <v>162</v>
       </c>
@@ -7866,10 +8300,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="13"/>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
       <c r="G13" s="26" t="s">
         <v>161</v>
       </c>
@@ -7884,9 +8323,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
       <c r="G14" s="10" t="s">
         <v>181</v>
       </c>
@@ -7901,9 +8345,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
       <c r="G15" s="26" t="s">
         <v>164</v>
       </c>
@@ -7918,9 +8367,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="G16" s="20" t="s">
         <v>180</v>
       </c>
@@ -7934,7 +8386,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="20" t="s">
         <v>189</v>
       </c>
@@ -7948,7 +8406,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="21" t="s">
         <v>165</v>
       </c>
@@ -7962,7 +8426,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="K19" s="43" t="s">
@@ -7972,7 +8442,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="28"/>
       <c r="H20" s="28"/>
       <c r="K20" s="19" t="s">
@@ -7982,73 +8458,77 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="K22" s="28"/>
       <c r="L22" s="28"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="K23" s="28"/>
       <c r="L23" s="28"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
       <c r="K24" s="28"/>
       <c r="L24" s="28"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="K25" s="28"/>
       <c r="L25" s="28"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="K26" s="28"/>
       <c r="L26" s="28"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="K27" s="28"/>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="K29" s="28"/>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="K30" s="28"/>
       <c r="L30" s="28"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="K31" s="28"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
       <c r="K32" s="28"/>
